--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -2538,7 +2538,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128962039</v>
+        <v>128962472</v>
       </c>
       <c r="B19" t="n">
         <v>8450</v>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463930</v>
+        <v>463970</v>
       </c>
       <c r="R19" t="n">
-        <v>6766330</v>
+        <v>6766411</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128962472</v>
+        <v>128962039</v>
       </c>
       <c r="B20" t="n">
         <v>8450</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463970</v>
+        <v>463930</v>
       </c>
       <c r="R20" t="n">
-        <v>6766411</v>
+        <v>6766330</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,45 +2863,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962071</v>
+        <v>128962460</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463954</v>
+        <v>463970</v>
       </c>
       <c r="R22" t="n">
-        <v>6766328</v>
+        <v>6766411</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962460</v>
+        <v>128963084</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,39 +2986,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463970</v>
+        <v>464006</v>
       </c>
       <c r="R23" t="n">
-        <v>6766411</v>
+        <v>6766426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,32 +3082,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963084</v>
+        <v>128962071</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464006</v>
+        <v>463954</v>
       </c>
       <c r="R24" t="n">
-        <v>6766426</v>
+        <v>6766328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R10" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B11" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R11" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128957279</v>
+        <v>128961985</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>79743</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,39 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464061</v>
+        <v>463919</v>
       </c>
       <c r="R16" t="n">
-        <v>6766452</v>
+        <v>6766325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,7 +2314,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128956694</v>
+        <v>128957279</v>
       </c>
       <c r="B17" t="n">
         <v>57717</v>
@@ -2350,7 +2345,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2359,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464077</v>
+        <v>464061</v>
       </c>
       <c r="R17" t="n">
-        <v>6766527</v>
+        <v>6766452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128961985</v>
+        <v>128956694</v>
       </c>
       <c r="B18" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,34 +2437,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463919</v>
+        <v>464077</v>
       </c>
       <c r="R18" t="n">
-        <v>6766325</v>
+        <v>6766527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128963411</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128963099</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128962562</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128962683</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128962193</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128962735</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128957818</v>
       </c>
       <c r="B10" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128962371</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>128963311</v>
       </c>
       <c r="B12" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128962011</v>
+        <v>128963948</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,27 +1883,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463930</v>
+        <v>464006</v>
       </c>
       <c r="R13" t="n">
-        <v>6766330</v>
+        <v>6766454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128963948</v>
+        <v>128962011</v>
       </c>
       <c r="B14" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,31 +1999,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464006</v>
+        <v>463930</v>
       </c>
       <c r="R14" t="n">
-        <v>6766454</v>
+        <v>6766330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128961985</v>
       </c>
       <c r="B16" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128957279</v>
       </c>
       <c r="B17" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128956694</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962460</v>
+        <v>128963084</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,39 +2874,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463970</v>
+        <v>464006</v>
       </c>
       <c r="R22" t="n">
-        <v>6766411</v>
+        <v>6766426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,34 +2981,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R23" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3192,7 +3192,7 @@
         <v>128963329</v>
       </c>
       <c r="B25" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R4" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R5" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R10" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R11" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128957279</v>
+        <v>128961985</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,39 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464061</v>
+        <v>463919</v>
       </c>
       <c r="R16" t="n">
-        <v>6766452</v>
+        <v>6766325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,7 +2314,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128956694</v>
+        <v>128957279</v>
       </c>
       <c r="B17" t="n">
         <v>57720</v>
@@ -2350,7 +2345,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2359,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464077</v>
+        <v>464061</v>
       </c>
       <c r="R17" t="n">
-        <v>6766527</v>
+        <v>6766452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128961985</v>
+        <v>128956694</v>
       </c>
       <c r="B18" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,34 +2437,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463919</v>
+        <v>464077</v>
       </c>
       <c r="R18" t="n">
-        <v>6766325</v>
+        <v>6766527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128963084</v>
+        <v>128962071</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464006</v>
+        <v>463954</v>
       </c>
       <c r="R22" t="n">
-        <v>6766426</v>
+        <v>6766328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962460</v>
+        <v>128963084</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,39 +2981,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463970</v>
+        <v>464006</v>
       </c>
       <c r="R23" t="n">
-        <v>6766411</v>
+        <v>6766426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,45 +3077,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128962071</v>
+        <v>128962460</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463954</v>
+        <v>463970</v>
       </c>
       <c r="R24" t="n">
-        <v>6766328</v>
+        <v>6766411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128963411</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128963099</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128962735</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R10" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R11" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>128963311</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128961985</v>
+        <v>128957279</v>
       </c>
       <c r="B16" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,34 +2218,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463919</v>
+        <v>464061</v>
       </c>
       <c r="R16" t="n">
-        <v>6766325</v>
+        <v>6766452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,7 +2319,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128957279</v>
+        <v>128956694</v>
       </c>
       <c r="B17" t="n">
         <v>57720</v>
@@ -2345,7 +2350,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2354,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464061</v>
+        <v>464077</v>
       </c>
       <c r="R17" t="n">
-        <v>6766452</v>
+        <v>6766527</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128956694</v>
+        <v>128961985</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,39 +2442,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464077</v>
+        <v>463919</v>
       </c>
       <c r="R18" t="n">
-        <v>6766527</v>
+        <v>6766325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962071</v>
+        <v>128963084</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463954</v>
+        <v>464006</v>
       </c>
       <c r="R22" t="n">
-        <v>6766328</v>
+        <v>6766426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,34 +2981,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R23" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,50 +3082,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128962460</v>
+        <v>128962071</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463970</v>
+        <v>463954</v>
       </c>
       <c r="R24" t="n">
-        <v>6766411</v>
+        <v>6766328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,7 +3192,7 @@
         <v>128963329</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R4" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B5" t="n">
-        <v>79625</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R5" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R10" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R11" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B4" t="n">
-        <v>79625</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R4" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R5" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R10" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R11" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128957279</v>
+        <v>128961985</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,39 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464061</v>
+        <v>463919</v>
       </c>
       <c r="R16" t="n">
-        <v>6766452</v>
+        <v>6766325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,7 +2314,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128956694</v>
+        <v>128957279</v>
       </c>
       <c r="B17" t="n">
         <v>57720</v>
@@ -2350,7 +2345,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2359,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464077</v>
+        <v>464061</v>
       </c>
       <c r="R17" t="n">
-        <v>6766527</v>
+        <v>6766452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128961985</v>
+        <v>128956694</v>
       </c>
       <c r="B18" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,34 +2437,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463919</v>
+        <v>464077</v>
       </c>
       <c r="R18" t="n">
-        <v>6766325</v>
+        <v>6766527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R10" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R11" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128961985</v>
+        <v>128957279</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,34 +2218,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463919</v>
+        <v>464061</v>
       </c>
       <c r="R16" t="n">
-        <v>6766325</v>
+        <v>6766452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128957279</v>
+        <v>128961985</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,39 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464061</v>
+        <v>463919</v>
       </c>
       <c r="R17" t="n">
-        <v>6766452</v>
+        <v>6766325</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,34 +2874,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R22" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962460</v>
+        <v>128963084</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,39 +2986,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463970</v>
+        <v>464006</v>
       </c>
       <c r="R23" t="n">
-        <v>6766411</v>
+        <v>6766426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128963411</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128963099</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128962562</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128962683</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128962193</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128962735</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R10" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R11" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>128963311</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128962011</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128963948</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128957279</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128961985</v>
+        <v>128956694</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>57722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2330,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463919</v>
+        <v>464077</v>
       </c>
       <c r="R17" t="n">
-        <v>6766325</v>
+        <v>6766527</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2394,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2404,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128956694</v>
+        <v>128961985</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,39 +2442,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464077</v>
+        <v>463919</v>
       </c>
       <c r="R18" t="n">
-        <v>6766527</v>
+        <v>6766325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>128962460</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>128963084</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>128963329</v>
       </c>
       <c r="B25" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -2863,50 +2863,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962460</v>
+        <v>128962071</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463970</v>
+        <v>463954</v>
       </c>
       <c r="R22" t="n">
-        <v>6766411</v>
+        <v>6766328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,34 +2981,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R23" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,32 +3082,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128962071</v>
+        <v>128963084</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463954</v>
+        <v>464006</v>
       </c>
       <c r="R24" t="n">
-        <v>6766328</v>
+        <v>6766426</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128962011</v>
+        <v>128963948</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>57885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,27 +1883,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463930</v>
+        <v>464006</v>
       </c>
       <c r="R13" t="n">
-        <v>6766330</v>
+        <v>6766454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128963948</v>
+        <v>128962011</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,31 +1999,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464006</v>
+        <v>463930</v>
       </c>
       <c r="R14" t="n">
-        <v>6766454</v>
+        <v>6766330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962071</v>
+        <v>128963084</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463954</v>
+        <v>464006</v>
       </c>
       <c r="R22" t="n">
-        <v>6766328</v>
+        <v>6766426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,50 +2970,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962460</v>
+        <v>128962071</v>
       </c>
       <c r="B23" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463970</v>
+        <v>463954</v>
       </c>
       <c r="R23" t="n">
-        <v>6766411</v>
+        <v>6766328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,10 +3077,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,34 +3088,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R24" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128963411</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128963099</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R4" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R5" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128962562</v>
+        <v>128962683</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463975</v>
+        <v>463995</v>
       </c>
       <c r="R6" t="n">
-        <v>6766375</v>
+        <v>6766385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128962683</v>
+        <v>128962562</v>
       </c>
       <c r="B7" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463995</v>
+        <v>463975</v>
       </c>
       <c r="R7" t="n">
-        <v>6766385</v>
+        <v>6766375</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
         <v>128962193</v>
       </c>
       <c r="B8" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128962735</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R10" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R11" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>128963311</v>
       </c>
       <c r="B12" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963948</v>
+        <v>128962011</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,31 +1883,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1916,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464006</v>
+        <v>463930</v>
       </c>
       <c r="R13" t="n">
-        <v>6766454</v>
+        <v>6766330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128962011</v>
+        <v>128963948</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,27 +1995,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463930</v>
+        <v>464006</v>
       </c>
       <c r="R14" t="n">
-        <v>6766330</v>
+        <v>6766454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128957279</v>
+        <v>128961985</v>
       </c>
       <c r="B16" t="n">
-        <v>57722</v>
+        <v>79660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,39 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464061</v>
+        <v>463919</v>
       </c>
       <c r="R16" t="n">
-        <v>6766452</v>
+        <v>6766325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2314,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128956694</v>
+        <v>128957279</v>
       </c>
       <c r="B17" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2345,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2359,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464077</v>
+        <v>464061</v>
       </c>
       <c r="R17" t="n">
-        <v>6766527</v>
+        <v>6766452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128961985</v>
+        <v>128956694</v>
       </c>
       <c r="B18" t="n">
-        <v>79658</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,34 +2437,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463919</v>
+        <v>464077</v>
       </c>
       <c r="R18" t="n">
-        <v>6766325</v>
+        <v>6766527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>128963084</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2970,45 +2970,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962071</v>
+        <v>128962460</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463954</v>
+        <v>463970</v>
       </c>
       <c r="R23" t="n">
-        <v>6766328</v>
+        <v>6766411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,50 +3082,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128962460</v>
+        <v>128962071</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463970</v>
+        <v>463954</v>
       </c>
       <c r="R24" t="n">
-        <v>6766411</v>
+        <v>6766328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,7 +3192,7 @@
         <v>128963329</v>
       </c>
       <c r="B25" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B4" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R4" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R5" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128962683</v>
+        <v>128962562</v>
       </c>
       <c r="B6" t="n">
         <v>57724</v>
@@ -1134,7 +1134,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463995</v>
+        <v>463975</v>
       </c>
       <c r="R6" t="n">
-        <v>6766385</v>
+        <v>6766375</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128962562</v>
+        <v>128962683</v>
       </c>
       <c r="B7" t="n">
         <v>57724</v>
@@ -1246,7 +1246,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463975</v>
+        <v>463995</v>
       </c>
       <c r="R7" t="n">
-        <v>6766375</v>
+        <v>6766385</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,34 +2874,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R22" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,50 +2975,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962460</v>
+        <v>128962071</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463970</v>
+        <v>463954</v>
       </c>
       <c r="R23" t="n">
-        <v>6766411</v>
+        <v>6766328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,32 +3082,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128962071</v>
+        <v>128963084</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463954</v>
+        <v>464006</v>
       </c>
       <c r="R24" t="n">
-        <v>6766328</v>
+        <v>6766426</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R10" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R11" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128962011</v>
+        <v>128963948</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,27 +1883,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463930</v>
+        <v>464006</v>
       </c>
       <c r="R13" t="n">
-        <v>6766330</v>
+        <v>6766454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128963948</v>
+        <v>128962011</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,31 +1999,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464006</v>
+        <v>463930</v>
       </c>
       <c r="R14" t="n">
-        <v>6766454</v>
+        <v>6766330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R4" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B5" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R5" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R10" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R11" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963948</v>
+        <v>128962011</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,31 +1883,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1916,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464006</v>
+        <v>463930</v>
       </c>
       <c r="R13" t="n">
-        <v>6766454</v>
+        <v>6766330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128962011</v>
+        <v>128963948</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,27 +1995,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463930</v>
+        <v>464006</v>
       </c>
       <c r="R14" t="n">
-        <v>6766330</v>
+        <v>6766454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,50 +2863,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962460</v>
+        <v>128962071</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463970</v>
+        <v>463954</v>
       </c>
       <c r="R22" t="n">
-        <v>6766411</v>
+        <v>6766328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,32 +2970,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962071</v>
+        <v>128963084</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3010,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463954</v>
+        <v>464006</v>
       </c>
       <c r="R23" t="n">
-        <v>6766328</v>
+        <v>6766426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,10 +3077,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,34 +3088,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R24" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B4" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R4" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R5" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128961985</v>
+        <v>128957279</v>
       </c>
       <c r="B16" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,34 +2218,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463919</v>
+        <v>464061</v>
       </c>
       <c r="R16" t="n">
-        <v>6766325</v>
+        <v>6766452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,7 +2319,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128957279</v>
+        <v>128956694</v>
       </c>
       <c r="B17" t="n">
         <v>57724</v>
@@ -2345,7 +2350,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2354,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464061</v>
+        <v>464077</v>
       </c>
       <c r="R17" t="n">
-        <v>6766452</v>
+        <v>6766527</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128956694</v>
+        <v>128961985</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,39 +2442,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464077</v>
+        <v>463919</v>
       </c>
       <c r="R18" t="n">
-        <v>6766527</v>
+        <v>6766325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962071</v>
+        <v>128963084</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463954</v>
+        <v>464006</v>
       </c>
       <c r="R22" t="n">
-        <v>6766328</v>
+        <v>6766426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,34 +2981,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R23" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,50 +3082,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128962460</v>
+        <v>128962071</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463970</v>
+        <v>463954</v>
       </c>
       <c r="R24" t="n">
-        <v>6766411</v>
+        <v>6766328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R10" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R11" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128957279</v>
+        <v>128961985</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,39 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464061</v>
+        <v>463919</v>
       </c>
       <c r="R16" t="n">
-        <v>6766452</v>
+        <v>6766325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,7 +2314,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128956694</v>
+        <v>128957279</v>
       </c>
       <c r="B17" t="n">
         <v>57724</v>
@@ -2350,7 +2345,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2359,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464077</v>
+        <v>464061</v>
       </c>
       <c r="R17" t="n">
-        <v>6766527</v>
+        <v>6766452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128961985</v>
+        <v>128956694</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,34 +2437,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463919</v>
+        <v>464077</v>
       </c>
       <c r="R18" t="n">
-        <v>6766325</v>
+        <v>6766527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,34 +2874,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R22" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962460</v>
+        <v>128963084</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,39 +2986,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463970</v>
+        <v>464006</v>
       </c>
       <c r="R23" t="n">
-        <v>6766411</v>
+        <v>6766426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128963411</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128963099</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128962735</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R10" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R11" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>128963311</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128961985</v>
       </c>
       <c r="B16" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962460</v>
+        <v>128963084</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,39 +2874,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463970</v>
+        <v>464006</v>
       </c>
       <c r="R22" t="n">
-        <v>6766411</v>
+        <v>6766426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,34 +2981,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R23" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3192,7 +3192,7 @@
         <v>128963329</v>
       </c>
       <c r="B25" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128963411</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128963099</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128962735</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128962371</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>128963311</v>
       </c>
       <c r="B12" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128961985</v>
+        <v>128956694</v>
       </c>
       <c r="B16" t="n">
-        <v>79662</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,34 +2218,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463919</v>
+        <v>464077</v>
       </c>
       <c r="R16" t="n">
-        <v>6766325</v>
+        <v>6766527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128957279</v>
+        <v>128961985</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,39 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464061</v>
+        <v>463919</v>
       </c>
       <c r="R17" t="n">
-        <v>6766452</v>
+        <v>6766325</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,7 +2426,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128956694</v>
+        <v>128957279</v>
       </c>
       <c r="B18" t="n">
         <v>57724</v>
@@ -2457,7 +2457,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464077</v>
+        <v>464061</v>
       </c>
       <c r="R18" t="n">
-        <v>6766527</v>
+        <v>6766452</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>128963084</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>128963329</v>
       </c>
       <c r="B25" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128956694</v>
+        <v>128961985</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,39 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464077</v>
+        <v>463919</v>
       </c>
       <c r="R16" t="n">
-        <v>6766527</v>
+        <v>6766325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2314,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128961985</v>
+        <v>128957279</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2325,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463919</v>
+        <v>464061</v>
       </c>
       <c r="R17" t="n">
-        <v>6766325</v>
+        <v>6766452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,7 +2426,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128957279</v>
+        <v>128956694</v>
       </c>
       <c r="B18" t="n">
         <v>57724</v>
@@ -2457,7 +2457,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464061</v>
+        <v>464077</v>
       </c>
       <c r="R18" t="n">
-        <v>6766452</v>
+        <v>6766527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R4" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B5" t="n">
-        <v>79634</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R5" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R10" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R11" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
         <v>128963058</v>
       </c>
       <c r="B15" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>128957197</v>
       </c>
       <c r="B21" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128963084</v>
+        <v>128962460</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,34 +2874,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464006</v>
+        <v>463970</v>
       </c>
       <c r="R22" t="n">
-        <v>6766426</v>
+        <v>6766411</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128962460</v>
+        <v>128963084</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,39 +2986,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463970</v>
+        <v>464006</v>
       </c>
       <c r="R23" t="n">
-        <v>6766411</v>
+        <v>6766426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964090</v>
+        <v>128956700</v>
       </c>
       <c r="B4" t="n">
-        <v>79634</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464056</v>
+        <v>464077</v>
       </c>
       <c r="R4" t="n">
-        <v>6766481</v>
+        <v>6766527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128956700</v>
+        <v>128964090</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464077</v>
+        <v>464056</v>
       </c>
       <c r="R5" t="n">
-        <v>6766527</v>
+        <v>6766481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128957818</v>
+        <v>128962371</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464094</v>
+        <v>463959</v>
       </c>
       <c r="R10" t="n">
-        <v>6766427</v>
+        <v>6766416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128962371</v>
+        <v>128957818</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463959</v>
+        <v>464094</v>
       </c>
       <c r="R11" t="n">
-        <v>6766416</v>
+        <v>6766427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128961985</v>
+        <v>128957279</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,34 +2218,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463919</v>
+        <v>464061</v>
       </c>
       <c r="R16" t="n">
-        <v>6766325</v>
+        <v>6766452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,7 +2319,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128957279</v>
+        <v>128956694</v>
       </c>
       <c r="B17" t="n">
         <v>57724</v>
@@ -2345,7 +2350,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2354,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464061</v>
+        <v>464077</v>
       </c>
       <c r="R17" t="n">
-        <v>6766452</v>
+        <v>6766527</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128956694</v>
+        <v>128961985</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,39 +2442,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464077</v>
+        <v>463919</v>
       </c>
       <c r="R18" t="n">
-        <v>6766527</v>
+        <v>6766325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2863,50 +2863,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962460</v>
+        <v>128962071</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463970</v>
+        <v>463954</v>
       </c>
       <c r="R22" t="n">
-        <v>6766411</v>
+        <v>6766328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3082,45 +3077,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128962071</v>
+        <v>128962460</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463954</v>
+        <v>463970</v>
       </c>
       <c r="R24" t="n">
-        <v>6766328</v>
+        <v>6766411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128963411</v>
+        <v>128957197</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464006</v>
+        <v>464108</v>
       </c>
       <c r="R2" t="n">
-        <v>6766454</v>
+        <v>6766494</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963099</v>
+        <v>128963058</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464013</v>
+        <v>464006</v>
       </c>
       <c r="R3" t="n">
-        <v>6766435</v>
+        <v>6766426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,32 +893,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128956700</v>
+        <v>128962371</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464077</v>
+        <v>463959</v>
       </c>
       <c r="R4" t="n">
-        <v>6766527</v>
+        <v>6766416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128964090</v>
+        <v>128962735</v>
       </c>
       <c r="B5" t="n">
-        <v>79634</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464056</v>
+        <v>463980</v>
       </c>
       <c r="R5" t="n">
-        <v>6766481</v>
+        <v>6766365</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,50 +1107,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128962562</v>
+        <v>128963084</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463975</v>
+        <v>464006</v>
       </c>
       <c r="R6" t="n">
-        <v>6766375</v>
+        <v>6766426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,50 +1214,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128962683</v>
+        <v>128963099</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463995</v>
+        <v>464013</v>
       </c>
       <c r="R7" t="n">
-        <v>6766385</v>
+        <v>6766435</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,50 +1321,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128962193</v>
+        <v>128963411</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463924</v>
+        <v>464006</v>
       </c>
       <c r="R8" t="n">
-        <v>6766416</v>
+        <v>6766454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128962735</v>
+        <v>128963311</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463980</v>
+        <v>464006</v>
       </c>
       <c r="R9" t="n">
-        <v>6766365</v>
+        <v>6766454</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128962371</v>
+        <v>128961160</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1546,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463959</v>
+        <v>463987</v>
       </c>
       <c r="R10" t="n">
-        <v>6766416</v>
+        <v>6766274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128957818</v>
+        <v>128961985</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1653,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464094</v>
+        <v>463919</v>
       </c>
       <c r="R11" t="n">
-        <v>6766427</v>
+        <v>6766325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,45 +1749,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963311</v>
+        <v>128956569</v>
       </c>
       <c r="B12" t="n">
-        <v>78801</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464006</v>
+        <v>464111</v>
       </c>
       <c r="R12" t="n">
-        <v>6766454</v>
+        <v>6766558</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,14 +1861,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128962011</v>
+        <v>128956694</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1912,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463930</v>
+        <v>464077</v>
       </c>
       <c r="R13" t="n">
-        <v>6766330</v>
+        <v>6766527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,42 +1973,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128963948</v>
+        <v>128956774</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2028,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464006</v>
+        <v>464054</v>
       </c>
       <c r="R14" t="n">
-        <v>6766454</v>
+        <v>6766536</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128963058</v>
+        <v>128957279</v>
       </c>
       <c r="B15" t="n">
-        <v>92832</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,34 +2096,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464006</v>
+        <v>464061</v>
       </c>
       <c r="R15" t="n">
-        <v>6766426</v>
+        <v>6766452</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2160,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2170,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,14 +2197,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128957279</v>
+        <v>128957818</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2247,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464061</v>
+        <v>464094</v>
       </c>
       <c r="R16" t="n">
-        <v>6766452</v>
+        <v>6766427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2272,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2282,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,14 +2309,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128956694</v>
+        <v>128958240</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2359,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464077</v>
+        <v>464182</v>
       </c>
       <c r="R17" t="n">
-        <v>6766527</v>
+        <v>6766438</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2404,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,45 +2421,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128961985</v>
+        <v>128958576</v>
       </c>
       <c r="B18" t="n">
-        <v>79663</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463919</v>
+        <v>464174</v>
       </c>
       <c r="R18" t="n">
-        <v>6766325</v>
+        <v>6766418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,10 +2533,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128962472</v>
+        <v>128962011</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,34 +2544,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463970</v>
+        <v>463930</v>
       </c>
       <c r="R19" t="n">
-        <v>6766411</v>
+        <v>6766330</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128962039</v>
+        <v>128962193</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,34 +2656,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463930</v>
+        <v>463924</v>
       </c>
       <c r="R20" t="n">
-        <v>6766330</v>
+        <v>6766416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2752,10 +2757,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128957197</v>
+        <v>128962460</v>
       </c>
       <c r="B21" t="n">
-        <v>92832</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,26 +2768,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2791,10 +2797,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464108</v>
+        <v>463970</v>
       </c>
       <c r="R21" t="n">
-        <v>6766494</v>
+        <v>6766411</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,7 +2832,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2836,7 +2842,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,10 +2869,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128962071</v>
+        <v>128962562</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,34 +2880,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463954</v>
+        <v>463975</v>
       </c>
       <c r="R22" t="n">
-        <v>6766328</v>
+        <v>6766375</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,45 +2981,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128963084</v>
+        <v>128962683</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464006</v>
+        <v>463995</v>
       </c>
       <c r="R23" t="n">
-        <v>6766426</v>
+        <v>6766385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128962460</v>
+        <v>128961560</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,16 +3104,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3117,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463970</v>
+        <v>463979</v>
       </c>
       <c r="R24" t="n">
-        <v>6766411</v>
+        <v>6766276</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,10 +3205,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128963329</v>
+        <v>128958610</v>
       </c>
       <c r="B25" t="n">
-        <v>79634</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,34 +3216,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464006</v>
+        <v>464174</v>
       </c>
       <c r="R25" t="n">
-        <v>6766454</v>
+        <v>6766418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,6 +3318,987 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128960932</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>464014</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6766293</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128963948</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>464006</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6766454</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128956700</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>464077</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6766527</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128960668</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>464014</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6766293</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128962039</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>463930</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6766330</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128962071</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>463954</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6766328</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128962472</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>463970</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6766411</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128963329</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>464006</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6766454</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128964090</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>464056</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6766481</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46450-2025 artfynd.xlsx
+++ b/artfynd/A 46450-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128957197</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963058</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962735</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963084</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963411</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963311</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128961160</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128961985</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128956569</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128956694</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2082,6 +2147,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128956774</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2194,6 +2264,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128957279</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2306,6 +2381,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128957818</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2418,6 +2498,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128958240</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128958576</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2642,6 +2732,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962011</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2754,6 +2849,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962193</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2866,6 +2966,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962460</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2978,6 +3083,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962562</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3090,6 +3200,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962683</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,6 +3317,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128961560</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3318,6 +3438,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128958610</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3434,6 +3559,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128960932</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3550,6 +3680,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963948</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3657,6 +3792,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128956700</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3764,6 +3904,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128960668</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3871,6 +4016,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962039</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3978,6 +4128,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962071</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4085,6 +4240,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962472</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4192,6 +4352,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963329</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4299,8 +4464,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964090</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>